--- a/data/trans_orig/IP31KM05_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM05_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>43307</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37297</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>47257</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>80,62%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>69,44%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>87,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>40667</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>33472</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>46357</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>75,73%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>62,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>86,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>45928</t>
+          <t>35243</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38711</t>
+          <t>29485</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50902</t>
+          <t>39366</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>86594</t>
+          <t>78551</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76290</t>
+          <t>70782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94282</t>
+          <t>85412</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10408</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6458</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16418</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>19,38%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>30,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13032</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7342</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20227</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>24,27%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>13,67%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37,67%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12417</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19634</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>25449</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17761</t>
+          <t>14208</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35753</t>
+          <t>28838</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>386404</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>371272</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>400446</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>82,84%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>79,6%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>85,85%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>506</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>368267</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>352441</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>385789</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>81,51%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>78,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>85,38%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>518</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>415290</t>
+          <t>342674</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>396271</t>
+          <t>329172</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>430646</t>
+          <t>356757</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>783557</t>
+          <t>729079</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>757845</t>
+          <t>708541</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>808804</t>
+          <t>752923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>80019</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>65977</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>95151</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>17,16%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20,4%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>83565</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>66043</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>99391</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,49%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,62%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>22,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>89960</t>
+          <t>81992</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74604</t>
+          <t>67909</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108979</t>
+          <t>95494</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>173525</t>
+          <t>162011</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>138167</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>199237</t>
+          <t>182549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>136299</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>125883</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>144330</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>81,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>75,52%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>86,59%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>115926</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>106668</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>123320</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>79,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>72,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>147544</t>
+          <t>116940</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>136706</t>
+          <t>107229</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157584</t>
+          <t>124330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>263469</t>
+          <t>253238</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>249097</t>
+          <t>239932</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>275731</t>
+          <t>264195</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,19%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30387</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22356</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>40803</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>18,23%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13,41%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>24,48%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>30260</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22866</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>39518</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>20,7%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,64%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>27,03%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33595</t>
+          <t>30200</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23555</t>
+          <t>22810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44433</t>
+          <t>39911</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>63855</t>
+          <t>60587</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51593</t>
+          <t>49630</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78227</t>
+          <t>73893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>566010</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>547310</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>583530</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>82,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>79,69%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>84,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>733</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>524861</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>505067</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>545859</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>80,54%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>77,5%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>608760</t>
+          <t>494858</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>584740</t>
+          <t>478203</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>626642</t>
+          <t>511597</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1133621</t>
+          <t>1060868</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1103734</t>
+          <t>1034834</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1162372</t>
+          <t>1086219</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>120814</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>103294</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>139514</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>126856</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>105858</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>146650</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19,46%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>135973</t>
+          <t>122853</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>118091</t>
+          <t>106114</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159993</t>
+          <t>139508</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>262829</t>
+          <t>243667</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>234078</t>
+          <t>218316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>292716</t>
+          <t>269701</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
